--- a/output/yearly_total_coral_cover_iteration_90_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_90_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.252893102963818</v>
+        <v>1.249368628705572</v>
       </c>
       <c r="C3" t="n">
-        <v>4.632618925231685</v>
+        <v>4.619198434114631</v>
       </c>
       <c r="D3" t="n">
-        <v>6.052302884767983</v>
+        <v>6.122232773741483</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93781491296349</v>
+        <v>11.99079983656169</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.375829592093401</v>
+        <v>1.364716923661603</v>
       </c>
       <c r="C4" t="n">
-        <v>5.127113734398442</v>
+        <v>5.086853697325889</v>
       </c>
       <c r="D4" t="n">
-        <v>6.275376776395972</v>
+        <v>6.395413997382844</v>
       </c>
       <c r="E4" t="n">
-        <v>12.77832010288781</v>
+        <v>12.84698461837034</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.541182576599755</v>
+        <v>1.520601252681945</v>
       </c>
       <c r="C5" t="n">
-        <v>5.748839783755704</v>
+        <v>5.640137049299182</v>
       </c>
       <c r="D5" t="n">
-        <v>6.526488881373156</v>
+        <v>6.755938001759009</v>
       </c>
       <c r="E5" t="n">
-        <v>13.81651124172862</v>
+        <v>13.91667630374014</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.739017455260267</v>
+        <v>1.711807317245812</v>
       </c>
       <c r="C6" t="n">
-        <v>6.487618234597694</v>
+        <v>6.281951205260751</v>
       </c>
       <c r="D6" t="n">
-        <v>6.892669587742078</v>
+        <v>7.192923569374581</v>
       </c>
       <c r="E6" t="n">
-        <v>15.11930527760004</v>
+        <v>15.18668209188114</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.966222711836106</v>
+        <v>1.927410952556414</v>
       </c>
       <c r="C7" t="n">
-        <v>7.331794571701395</v>
+        <v>6.982966677995125</v>
       </c>
       <c r="D7" t="n">
-        <v>7.299570195561063</v>
+        <v>7.750787206238092</v>
       </c>
       <c r="E7" t="n">
-        <v>16.59758747909856</v>
+        <v>16.66116483678963</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.205437460759543</v>
+        <v>1.191153524522933</v>
       </c>
       <c r="C8" t="n">
-        <v>4.927805120054497</v>
+        <v>4.551504618396259</v>
       </c>
       <c r="D8" t="n">
-        <v>5.681323783666151</v>
+        <v>6.018021891590513</v>
       </c>
       <c r="E8" t="n">
-        <v>11.81456636448019</v>
+        <v>11.7606800345097</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.506817003038412</v>
+        <v>1.523806018216284</v>
       </c>
       <c r="C9" t="n">
-        <v>5.98826084346104</v>
+        <v>5.459314092201518</v>
       </c>
       <c r="D9" t="n">
-        <v>6.216191871204905</v>
+        <v>6.618853738586183</v>
       </c>
       <c r="E9" t="n">
-        <v>13.71126971770436</v>
+        <v>13.60197384900398</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.821427937633014</v>
+        <v>1.885255387896991</v>
       </c>
       <c r="C10" t="n">
-        <v>7.206876733133498</v>
+        <v>6.528861364734508</v>
       </c>
       <c r="D10" t="n">
-        <v>6.79151587290545</v>
+        <v>7.25993136956658</v>
       </c>
       <c r="E10" t="n">
-        <v>15.81982054367196</v>
+        <v>15.67404812219808</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.136853070549245</v>
+        <v>2.256985805684311</v>
       </c>
       <c r="C11" t="n">
-        <v>8.490432119331675</v>
+        <v>7.707167725775859</v>
       </c>
       <c r="D11" t="n">
-        <v>7.409969788138725</v>
+        <v>7.907829486053551</v>
       </c>
       <c r="E11" t="n">
-        <v>18.03725497801965</v>
+        <v>17.87198301751372</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.455126667502789</v>
+        <v>2.634079184076456</v>
       </c>
       <c r="C12" t="n">
-        <v>9.907391175831693</v>
+        <v>8.943967957104508</v>
       </c>
       <c r="D12" t="n">
-        <v>8.036109931400436</v>
+        <v>8.594853887992132</v>
       </c>
       <c r="E12" t="n">
-        <v>20.39862777473492</v>
+        <v>20.1729010291731</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.763908262708968</v>
+        <v>3.003815174051016</v>
       </c>
       <c r="C13" t="n">
-        <v>11.3485845090221</v>
+        <v>10.20835035609967</v>
       </c>
       <c r="D13" t="n">
-        <v>8.702197197067095</v>
+        <v>9.269782226160952</v>
       </c>
       <c r="E13" t="n">
-        <v>22.81468996879817</v>
+        <v>22.48194775631164</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.600209488014131</v>
+        <v>1.716134256931594</v>
       </c>
       <c r="C14" t="n">
-        <v>8.023833804286223</v>
+        <v>7.209984592419703</v>
       </c>
       <c r="D14" t="n">
-        <v>6.665320783580614</v>
+        <v>7.050931646854678</v>
       </c>
       <c r="E14" t="n">
-        <v>16.28936407588097</v>
+        <v>15.97705049620598</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.627904590750934</v>
+        <v>1.77999694509285</v>
       </c>
       <c r="C15" t="n">
-        <v>8.589124132391538</v>
+        <v>7.62512642663751</v>
       </c>
       <c r="D15" t="n">
-        <v>6.785673234644231</v>
+        <v>7.189475882877987</v>
       </c>
       <c r="E15" t="n">
-        <v>17.0027019577867</v>
+        <v>16.59459925460835</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.878917843772758</v>
+        <v>2.086567300698001</v>
       </c>
       <c r="C16" t="n">
-        <v>10.06897135186501</v>
+        <v>8.869393466999917</v>
       </c>
       <c r="D16" t="n">
-        <v>7.417418064850013</v>
+        <v>7.796981362265913</v>
       </c>
       <c r="E16" t="n">
-        <v>19.36530726048778</v>
+        <v>18.75294212996383</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.496851089711027</v>
+        <v>1.687310144334908</v>
       </c>
       <c r="C17" t="n">
-        <v>9.211944875965713</v>
+        <v>8.099340020219847</v>
       </c>
       <c r="D17" t="n">
-        <v>6.993754660559344</v>
+        <v>7.356579159617837</v>
       </c>
       <c r="E17" t="n">
-        <v>17.70255062623609</v>
+        <v>17.14322932417259</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.708918411305381</v>
+        <v>1.943732827207133</v>
       </c>
       <c r="C18" t="n">
-        <v>10.66806325342754</v>
+        <v>9.312004601982549</v>
       </c>
       <c r="D18" t="n">
-        <v>7.574743134455563</v>
+        <v>7.934151151503277</v>
       </c>
       <c r="E18" t="n">
-        <v>19.95172479918848</v>
+        <v>19.18988858069296</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.718078117386003</v>
+        <v>1.975109483834861</v>
       </c>
       <c r="C19" t="n">
-        <v>11.33826314120867</v>
+        <v>9.863059588376283</v>
       </c>
       <c r="D19" t="n">
-        <v>7.775736341946013</v>
+        <v>8.12974474662037</v>
       </c>
       <c r="E19" t="n">
-        <v>20.83207760054068</v>
+        <v>19.96791381883151</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.918816070473348</v>
+        <v>2.22773280309165</v>
       </c>
       <c r="C20" t="n">
-        <v>13.0142046471284</v>
+        <v>11.26206970188207</v>
       </c>
       <c r="D20" t="n">
-        <v>8.361054323217962</v>
+        <v>8.692924317161552</v>
       </c>
       <c r="E20" t="n">
-        <v>23.29407504081971</v>
+        <v>22.18272682213527</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.146720588468444</v>
+        <v>1.339692917215198</v>
       </c>
       <c r="C21" t="n">
-        <v>9.573591277779112</v>
+        <v>8.260484088394918</v>
       </c>
       <c r="D21" t="n">
-        <v>7.059188145047393</v>
+        <v>7.306834003443652</v>
       </c>
       <c r="E21" t="n">
-        <v>17.77950001129495</v>
+        <v>16.90701100905377</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_90_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_90_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.249368628705572</v>
+        <v>1.258243627951963</v>
       </c>
       <c r="C3" t="n">
-        <v>4.619198434114631</v>
+        <v>4.618707560262508</v>
       </c>
       <c r="D3" t="n">
-        <v>6.122232773741483</v>
+        <v>6.062542513323277</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99079983656169</v>
+        <v>11.93949370153775</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.364716923661603</v>
+        <v>1.39338295234027</v>
       </c>
       <c r="C4" t="n">
-        <v>5.086853697325889</v>
+        <v>5.112984873478407</v>
       </c>
       <c r="D4" t="n">
-        <v>6.395413997382844</v>
+        <v>6.286784650754018</v>
       </c>
       <c r="E4" t="n">
-        <v>12.84698461837034</v>
+        <v>12.7931524765727</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.520601252681945</v>
+        <v>1.574922082344633</v>
       </c>
       <c r="C5" t="n">
-        <v>5.640137049299182</v>
+        <v>5.742745120092255</v>
       </c>
       <c r="D5" t="n">
-        <v>6.755938001759009</v>
+        <v>6.588829194729653</v>
       </c>
       <c r="E5" t="n">
-        <v>13.91667630374014</v>
+        <v>13.90649639716654</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.711807317245812</v>
+        <v>1.781172107748283</v>
       </c>
       <c r="C6" t="n">
-        <v>6.281951205260751</v>
+        <v>6.516411025757602</v>
       </c>
       <c r="D6" t="n">
-        <v>7.192923569374581</v>
+        <v>6.897169441038644</v>
       </c>
       <c r="E6" t="n">
-        <v>15.18668209188114</v>
+        <v>15.19475257454453</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.927410952556414</v>
+        <v>2.006789664403807</v>
       </c>
       <c r="C7" t="n">
-        <v>6.982966677995125</v>
+        <v>7.416594606284449</v>
       </c>
       <c r="D7" t="n">
-        <v>7.750787206238092</v>
+        <v>7.233670580470032</v>
       </c>
       <c r="E7" t="n">
-        <v>16.66116483678963</v>
+        <v>16.65705485115829</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.191153524522933</v>
+        <v>1.22419898349705</v>
       </c>
       <c r="C8" t="n">
-        <v>4.551504618396259</v>
+        <v>5.075926889088636</v>
       </c>
       <c r="D8" t="n">
-        <v>6.018021891590513</v>
+        <v>5.502915925193913</v>
       </c>
       <c r="E8" t="n">
-        <v>11.7606800345097</v>
+        <v>11.8030417977796</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.523806018216284</v>
+        <v>1.523281842664304</v>
       </c>
       <c r="C9" t="n">
-        <v>5.459314092201518</v>
+        <v>6.246934020709558</v>
       </c>
       <c r="D9" t="n">
-        <v>6.618853738586183</v>
+        <v>6.065752121672847</v>
       </c>
       <c r="E9" t="n">
-        <v>13.60197384900398</v>
+        <v>13.83596798504671</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.885255387896991</v>
+        <v>1.842672422329093</v>
       </c>
       <c r="C10" t="n">
-        <v>6.528861364734508</v>
+        <v>7.612606104439014</v>
       </c>
       <c r="D10" t="n">
-        <v>7.25993136956658</v>
+        <v>6.627700915351005</v>
       </c>
       <c r="E10" t="n">
-        <v>15.67404812219808</v>
+        <v>16.08297944211911</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.256985805684311</v>
+        <v>2.17208473704205</v>
       </c>
       <c r="C11" t="n">
-        <v>7.707167725775859</v>
+        <v>9.129262065496533</v>
       </c>
       <c r="D11" t="n">
-        <v>7.907829486053551</v>
+        <v>7.228641002779042</v>
       </c>
       <c r="E11" t="n">
-        <v>17.87198301751372</v>
+        <v>18.52998780531762</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.634079184076456</v>
+        <v>2.501765831094848</v>
       </c>
       <c r="C12" t="n">
-        <v>8.943967957104508</v>
+        <v>10.75350549567748</v>
       </c>
       <c r="D12" t="n">
-        <v>8.594853887992132</v>
+        <v>7.890490070241403</v>
       </c>
       <c r="E12" t="n">
-        <v>20.1729010291731</v>
+        <v>21.14576139701373</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.003815174051016</v>
+        <v>2.806366664663053</v>
       </c>
       <c r="C13" t="n">
-        <v>10.20835035609967</v>
+        <v>12.46431760595329</v>
       </c>
       <c r="D13" t="n">
-        <v>9.269782226160952</v>
+        <v>8.410746431561174</v>
       </c>
       <c r="E13" t="n">
-        <v>22.48194775631164</v>
+        <v>23.68143070217752</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.716134256931594</v>
+        <v>1.621415238425862</v>
       </c>
       <c r="C14" t="n">
-        <v>7.209984592419703</v>
+        <v>8.777492064405372</v>
       </c>
       <c r="D14" t="n">
-        <v>7.050931646854678</v>
+        <v>6.44732370585261</v>
       </c>
       <c r="E14" t="n">
-        <v>15.97705049620598</v>
+        <v>16.84623100868384</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.77999694509285</v>
+        <v>1.640510231273463</v>
       </c>
       <c r="C15" t="n">
-        <v>7.62512642663751</v>
+        <v>9.613980378331824</v>
       </c>
       <c r="D15" t="n">
-        <v>7.189475882877987</v>
+        <v>6.534993775841851</v>
       </c>
       <c r="E15" t="n">
-        <v>16.59459925460835</v>
+        <v>17.78948438544714</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.086567300698001</v>
+        <v>1.878171715517531</v>
       </c>
       <c r="C16" t="n">
-        <v>8.869393466999917</v>
+        <v>11.42158406886809</v>
       </c>
       <c r="D16" t="n">
-        <v>7.796981362265913</v>
+        <v>7.076584714366647</v>
       </c>
       <c r="E16" t="n">
-        <v>18.75294212996383</v>
+        <v>20.37634049875227</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.687310144334908</v>
+        <v>1.48755393895181</v>
       </c>
       <c r="C17" t="n">
-        <v>8.099340020219847</v>
+        <v>10.59455980281058</v>
       </c>
       <c r="D17" t="n">
-        <v>7.356579159617837</v>
+        <v>6.622536218629539</v>
       </c>
       <c r="E17" t="n">
-        <v>17.14322932417259</v>
+        <v>18.70464996039193</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.943732827207133</v>
+        <v>1.681576737742107</v>
       </c>
       <c r="C18" t="n">
-        <v>9.312004601982549</v>
+        <v>12.41460223675966</v>
       </c>
       <c r="D18" t="n">
-        <v>7.934151151503277</v>
+        <v>7.084536870771045</v>
       </c>
       <c r="E18" t="n">
-        <v>19.18988858069296</v>
+        <v>21.18071584527281</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.975109483834861</v>
+        <v>1.672348309322187</v>
       </c>
       <c r="C19" t="n">
-        <v>9.863059588376283</v>
+        <v>13.31122259757123</v>
       </c>
       <c r="D19" t="n">
-        <v>8.12974474662037</v>
+        <v>7.209984592419703</v>
       </c>
       <c r="E19" t="n">
-        <v>19.96791381883151</v>
+        <v>22.19355549931312</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.22773280309165</v>
+        <v>1.851124566265531</v>
       </c>
       <c r="C20" t="n">
-        <v>11.26206970188207</v>
+        <v>15.31658954565098</v>
       </c>
       <c r="D20" t="n">
-        <v>8.692924317161552</v>
+        <v>7.681881261420017</v>
       </c>
       <c r="E20" t="n">
-        <v>22.18272682213527</v>
+        <v>24.84959537333653</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.339692917215198</v>
+        <v>1.097809917842868</v>
       </c>
       <c r="C21" t="n">
-        <v>8.260484088394918</v>
+        <v>11.26054799294049</v>
       </c>
       <c r="D21" t="n">
-        <v>7.306834003443652</v>
+        <v>6.440363114629502</v>
       </c>
       <c r="E21" t="n">
-        <v>16.90701100905377</v>
+        <v>18.79872102541286</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_90_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_90_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.258243627951963</v>
+        <v>2.585814982622161</v>
       </c>
       <c r="C3" t="n">
-        <v>4.618707560262508</v>
+        <v>7.653535374554918</v>
       </c>
       <c r="D3" t="n">
-        <v>6.062542513323277</v>
+        <v>8.21271005016369</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93949370153775</v>
+        <v>18.45206040734077</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.39338295234027</v>
+        <v>1.056208590454102</v>
       </c>
       <c r="C4" t="n">
-        <v>5.112984873478407</v>
+        <v>4.363757487660177</v>
       </c>
       <c r="D4" t="n">
-        <v>6.286784650754018</v>
+        <v>5.833015057562068</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7931524765727</v>
+        <v>11.25298113567635</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.574922082344633</v>
+        <v>1.130478543753665</v>
       </c>
       <c r="C5" t="n">
-        <v>5.742745120092255</v>
+        <v>4.843120294795154</v>
       </c>
       <c r="D5" t="n">
-        <v>6.588829194729653</v>
+        <v>6.122340497546395</v>
       </c>
       <c r="E5" t="n">
-        <v>13.90649639716654</v>
+        <v>12.09593933609521</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.781172107748283</v>
+        <v>1.220611092308383</v>
       </c>
       <c r="C6" t="n">
-        <v>6.516411025757602</v>
+        <v>5.426710268745032</v>
       </c>
       <c r="D6" t="n">
-        <v>6.897169441038644</v>
+        <v>6.460317831988037</v>
       </c>
       <c r="E6" t="n">
-        <v>15.19475257454453</v>
+        <v>13.10763919304145</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.006789664403807</v>
+        <v>1.327230133340779</v>
       </c>
       <c r="C7" t="n">
-        <v>7.416594606284449</v>
+        <v>6.140963728985007</v>
       </c>
       <c r="D7" t="n">
-        <v>7.233670580470032</v>
+        <v>6.896235183493284</v>
       </c>
       <c r="E7" t="n">
-        <v>16.65705485115829</v>
+        <v>14.36442904581907</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.22419898349705</v>
+        <v>1.440198599298519</v>
       </c>
       <c r="C8" t="n">
-        <v>5.075926889088636</v>
+        <v>6.964249944831221</v>
       </c>
       <c r="D8" t="n">
-        <v>5.502915925193913</v>
+        <v>7.433718573509663</v>
       </c>
       <c r="E8" t="n">
-        <v>11.8030417977796</v>
+        <v>15.8381671176394</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.523281842664304</v>
+        <v>1.558949202088388</v>
       </c>
       <c r="C9" t="n">
-        <v>6.246934020709558</v>
+        <v>7.957222325795934</v>
       </c>
       <c r="D9" t="n">
-        <v>6.065752121672847</v>
+        <v>7.939697357845194</v>
       </c>
       <c r="E9" t="n">
-        <v>13.83596798504671</v>
+        <v>17.45586888572952</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.842672422329093</v>
+        <v>0.9917713483071704</v>
       </c>
       <c r="C10" t="n">
-        <v>7.612606104439014</v>
+        <v>6.074033776266846</v>
       </c>
       <c r="D10" t="n">
-        <v>6.627700915351005</v>
+        <v>6.293807817339537</v>
       </c>
       <c r="E10" t="n">
-        <v>16.08297944211911</v>
+        <v>13.35961294191355</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.17208473704205</v>
+        <v>0.9223519681398784</v>
       </c>
       <c r="C11" t="n">
-        <v>9.129262065496533</v>
+        <v>6.326048411947003</v>
       </c>
       <c r="D11" t="n">
-        <v>7.228641002779042</v>
+        <v>6.227196235606391</v>
       </c>
       <c r="E11" t="n">
-        <v>18.52998780531762</v>
+        <v>13.47559661569327</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.501765831094848</v>
+        <v>0.9960910382058562</v>
       </c>
       <c r="C12" t="n">
-        <v>10.75350549567748</v>
+        <v>7.441775225392374</v>
       </c>
       <c r="D12" t="n">
-        <v>7.890490070241403</v>
+        <v>6.704934303446974</v>
       </c>
       <c r="E12" t="n">
-        <v>21.14576139701373</v>
+        <v>15.1428005670452</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.806366664663053</v>
+        <v>0.7920740477863266</v>
       </c>
       <c r="C13" t="n">
-        <v>12.46431760595329</v>
+        <v>7.109168920670598</v>
       </c>
       <c r="D13" t="n">
-        <v>8.410746431561174</v>
+        <v>6.191224999722787</v>
       </c>
       <c r="E13" t="n">
-        <v>23.68143070217752</v>
+        <v>14.09246796817971</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.621415238425862</v>
+        <v>0.8637907175815562</v>
       </c>
       <c r="C14" t="n">
-        <v>8.777492064405372</v>
+        <v>8.338022522076329</v>
       </c>
       <c r="D14" t="n">
-        <v>6.44732370585261</v>
+        <v>6.665566220506676</v>
       </c>
       <c r="E14" t="n">
-        <v>16.84623100868384</v>
+        <v>15.86737946016456</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.640510231273463</v>
+        <v>0.8407196465317562</v>
       </c>
       <c r="C15" t="n">
-        <v>9.613980378331824</v>
+        <v>9.032972269481519</v>
       </c>
       <c r="D15" t="n">
-        <v>6.534993775841851</v>
+        <v>6.784603129646603</v>
       </c>
       <c r="E15" t="n">
-        <v>17.78948438544714</v>
+        <v>16.65829504565988</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.878171715517531</v>
+        <v>0.9240405741911829</v>
       </c>
       <c r="C16" t="n">
-        <v>11.42158406886809</v>
+        <v>10.63835556789703</v>
       </c>
       <c r="D16" t="n">
-        <v>7.076584714366647</v>
+        <v>7.362989972126568</v>
       </c>
       <c r="E16" t="n">
-        <v>20.37634049875227</v>
+        <v>18.92538611421478</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.48755393895181</v>
+        <v>0.559262397201238</v>
       </c>
       <c r="C17" t="n">
-        <v>10.59455980281058</v>
+        <v>8.115587944725132</v>
       </c>
       <c r="D17" t="n">
-        <v>6.622536218629539</v>
+        <v>6.191617698804487</v>
       </c>
       <c r="E17" t="n">
-        <v>18.70464996039193</v>
+        <v>14.86646804073086</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.681576737742107</v>
+        <v>0.43707407793068</v>
       </c>
       <c r="C18" t="n">
-        <v>12.41460223675966</v>
+        <v>7.260780218637433</v>
       </c>
       <c r="D18" t="n">
-        <v>7.084536870771045</v>
+        <v>5.725258086856124</v>
       </c>
       <c r="E18" t="n">
-        <v>21.18071584527281</v>
+        <v>13.42311238342424</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.672348309322187</v>
+        <v>0.5108327829507429</v>
       </c>
       <c r="C19" t="n">
-        <v>13.31122259757123</v>
+        <v>9.068285734403277</v>
       </c>
       <c r="D19" t="n">
-        <v>7.209984592419703</v>
+        <v>6.347293432266904</v>
       </c>
       <c r="E19" t="n">
-        <v>22.19355549931312</v>
+        <v>15.92641194962092</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.851124566265531</v>
+        <v>0.5812928156845365</v>
       </c>
       <c r="C20" t="n">
-        <v>15.31658954565098</v>
+        <v>11.00826828538019</v>
       </c>
       <c r="D20" t="n">
-        <v>7.681881261420017</v>
+        <v>6.91653038614329</v>
       </c>
       <c r="E20" t="n">
-        <v>24.84959537333653</v>
+        <v>18.50609148720801</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.097809917842868</v>
+        <v>0.6439577716466104</v>
       </c>
       <c r="C21" t="n">
-        <v>11.26054799294049</v>
+        <v>13.10775538586607</v>
       </c>
       <c r="D21" t="n">
-        <v>6.440363114629502</v>
+        <v>7.482134873513962</v>
       </c>
       <c r="E21" t="n">
-        <v>18.79872102541286</v>
+        <v>21.23384803102665</v>
       </c>
     </row>
   </sheetData>
